--- a/V32631 - Drew Smith Course Links.xlsx
+++ b/V32631 - Drew Smith Course Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geethapriyan\OneDrive - Packt\Documents\Modern-Apple-Platform-Administration---macOS-and-iOS-Essentials-2025-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://packtservices-my.sharepoint.com/personal/geethapriyan_packt_com/Documents/Documents/Modern-Apple-Platform-Administration---macOS-and-iOS-Essentials-2025-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB80007-5022-4368-99EE-52210A383D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{5AB80007-5022-4368-99EE-52210A383D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FC2EE88-8B15-4F1B-837D-2588542D9192}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{84D78192-083B-4FAD-9488-112209A19717}"/>
   </bookViews>
@@ -257,13 +257,13 @@
     <t>Managing Apple Intelligence on Device</t>
   </si>
   <si>
-    <t>video22_1</t>
-  </si>
-  <si>
     <t>Mac Admin Community</t>
   </si>
   <si>
     <t>Modern Apple Platform Administration - macOS and iOS Essentials (2025)</t>
+  </si>
+  <si>
+    <t>video23_1</t>
   </si>
 </sst>
 </file>
@@ -724,7 +724,7 @@
     <row r="1" spans="1:6" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1"/>
       <c r="B1" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1"/>
       <c r="F1" s="8"/>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="34" spans="1:6" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>30</v>
